--- a/docs/testing/BVA/Table_Point/Point/BVA_Point_TestCases.xlsx
+++ b/docs/testing/BVA/Table_Point/Point/BVA_Point_TestCases.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BVA Point TestCases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BVA Point 4n+1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design 4n+1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BVA Point 4n+1'!$A$1:$K$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -51,18 +54,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00B7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B7B7B7"/>
-      </bottom>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -71,11 +63,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,451 +431,862 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TC ID</t>
+          <t>Test Case ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Endpoint</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Trường hợp kiểm thử</t>
+          <t>Input phone</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Input orderId</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Expected Status</t>
+          <t>finalPrice (Order fixture)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Actual Status</t>
+          <t>Expected HTTP</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Kết quả</t>
+          <t>Expected Payload / Oracle</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Actual HTTP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>phone: Thiếu trường</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>{"orderId":1}</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BVA-POINT-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0900000000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{{orderBaselineId}}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{{priceBaseline}}</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>message + earnedPoints + totalPoints; point calculation matches</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Baseline; fixture must be PAID + COMPLETED + isPointsAdded=false.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>phone: Chuỗi rỗng ""</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"","orderId":1}</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BVA-POINT-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>{{orderPhoneMinId}}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Success payload; customer/point fields present</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Requires a real User record with this phone and eligible Order fixture.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>phone: Giá trị null</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":null,"orderId":1}</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BVA-POINT-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Min+1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0000000001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{{orderPhoneMin1Id}}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Success payload; customer/point fields present</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Requires a real User record with this phone and eligible Order fixture.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>orderId: Thiếu trường</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000"}</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BVA-POINT-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Max-1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9999999998</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{{orderPhoneMax1Id}}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Success payload; customer/point fields present</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Requires a real User record with this phone and eligible Order fixture.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>orderId: 0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000","orderId":0}</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BVA-POINT-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{{orderPhoneMaxId}}</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Success payload; customer/point fields present</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Requires a real User record with this phone and eligible Order fixture.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>orderId: -1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000","orderId":-1}</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Đúng expected</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BVA-POINT-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>finalPrice</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{{phoneFinalPriceMin}}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{{orderFinalPriceMinId}}</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>200</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>earnedPoints = Math.round(finalPrice*0.05); payload fields present</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>finalPrice is read from Order, not request body.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>orderId: null</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000","orderId":null}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 400</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BVA-POINT-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>finalPrice</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Min+1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{{phoneFinalPriceMin1}}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{{orderFinalPriceMin1Id}}</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>earnedPoints = Math.round(finalPrice*0.05); payload fields present</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>finalPrice is read from Order, not request body.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>orderId: Sai kiểu ("abc")</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000","orderId":"abc"}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Đúng expected</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BVA-POINT-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>finalPrice</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Max-1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{{phoneFinalPriceMax1}}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{{orderFinalPriceMax1Id}}</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>earnedPoints = Math.round(finalPrice*0.05); payload fields present</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>finalPrice is read from Order, not request body.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TB_BVA_POINT_009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>/api/points/add-points</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Dữ liệu hợp lệ</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>{"phone":"0900000000","orderId":1}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BVA-POINT-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>finalPrice</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{{phoneFinalPriceMax}}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{{orderFinalPriceMaxId}}</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G10" t="n">
         <v>200</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Actual 404 thay vì expected 200</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>earnedPoints = Math.round(finalPrice*0.05); payload fields present</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>finalPrice is read from Order, not request body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BVA-POINT-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>orderId</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{{phoneOrderMin}}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Success payload; order accepted when fixture is eligible</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Requires Order #1 or equivalent fixture with required status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BVA-POINT-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>orderId</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Min+1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{{phoneOrderMin1}}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Success payload; order accepted when fixture is eligible</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Requires Order #2 or equivalent fixture with required status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BVA-POINT-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>orderId</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Max-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{{phoneOrderMax1}}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>999999</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Success payload; order accepted when fixture is eligible</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Requires a real eligible order with this ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BVA-POINT-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>orderId</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{{phoneOrderMax}}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fixture</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>200</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Success payload; order accepted when fixture is eligible</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NOT RUN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Requires a real eligible order with this ID.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Thiết kế</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Công thức</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4n + 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Số biến BVA (n)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3: phone, finalPrice, orderId</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tổng testcase</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mỗi biến</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4 điểm: Min, Min+1, Max-1, Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10 chữ số: 0000000000 .. 9999999999 (theo bộ thiết kế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>finalPrice</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0 .. 1,000,000 (theo bộ thiết kế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>orderId</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1 .. 1,000,000 (theo bộ thiết kế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lưu ý</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>finalPrice là thuộc tính của Order; Postman phải dùng Order fixture tương ứng.</t>
         </is>
       </c>
     </row>
